--- a/output/FH6_Tier_List.xlsx
+++ b/output/FH6_Tier_List.xlsx
@@ -12,12 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Reference" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tuning" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changelog" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tier List'!$A$1:$M$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tuning'!$A$33:$E$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Changelog'!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tier List'!$A$1:$M$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tuning'!$A$46:$E$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +63,18 @@
     <font>
       <color rgb="00000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00B45309"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -164,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -232,9 +242,22 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -600,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -617,7 +640,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Launch-window meta (curated ~9 days post-launch, late May 2026).</t>
+          <t>Launch-window meta, curated + web-refreshed (late May 2026).</t>
         </is>
       </c>
     </row>
@@ -657,181 +680,157 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Data origin</t>
+          <t>Read this first</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Seeded from curated guide; refreshable via free web search.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Read this first</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Launch-window snapshot, not a settled meta. Rankings will shift as players grind and post tunes. Re-verify high-cost buys against in-game leaderboards and the Find Tuning Setups marketplace.</t>
+          <t>Launch-window snapshot, not a settled meta. Rankings will shift as players grind and post tunes. Exact per-car PI is rarely published yet, so the PI column shows each class's band (your build target). Re-verify high-cost buys in-game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Confidence key</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Confidence key</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Multiple independent reputable sources agree.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Strong</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Multiple independent reputable sources agree.</t>
+          <t>Appears across guides but with disagreement or single-source weighting.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Tentative</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Appears across guides but with disagreement or single-source weighting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Tentative</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Early / contested; verify in-game before committing credits.</t>
+          <t>Early / contested / snippet-only; verify in-game before committing credits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Class tiers (low -&gt; high)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Class tiers (low -&gt; high)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Sheets</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Sheets</t>
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Tier List</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Every ranked car with its in-game PI number. Use the filter arrows to sort by class, PI, price, confidence, or discipline.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Tier List</t>
+          <t>Quick Reference</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Every ranked car. Use the filter arrows to sort by class, price, confidence, discipline.</t>
+          <t>Discipline x class grid — the top pick in each cell, colour coded.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Quick Reference</t>
+          <t>Tuning</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Discipline x class grid — the top pick in each cell, colour coded.</t>
+          <t>Per-discipline baseline setups, the FH6 Mechanical Balance stat, per-car tune notes, and where to get real tune codes (marked *).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Tuning</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Per-discipline baseline setups, the FH6 Mechanical Balance stat, per-car tune notes, and how to get REAL codes in-game.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
           <t>What was cross-referenced, and which low-quality sites to distrust.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Changelog</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Auto-appended each time you run a web refresh.</t>
         </is>
       </c>
     </row>
@@ -850,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -896,7 +895,7 @@
       </c>
       <c r="F1" s="15" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PI band</t>
         </is>
       </c>
       <c r="G1" s="15" t="inlineStr">
@@ -959,7 +958,7 @@
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>R 999</t>
+          <t>999</t>
         </is>
       </c>
       <c r="G2" s="18" t="n">
@@ -977,18 +976,18 @@
       </c>
       <c r="J2" s="17" t="inlineStr">
         <is>
-          <t>Cleanest R-Class consensus; superb stock speed, handling &amp; braking; only improves tuned.</t>
+          <t>Cleanest R consensus; superb stock speed, handling &amp; braking; only improves tuned.</t>
         </is>
       </c>
       <c r="K2" s="17" t="inlineStr">
         <is>
-          <t>Power can overwhelm you on tight tracks.</t>
+          <t>Power can overwhelm on tight tracks; track-focused.</t>
         </is>
       </c>
       <c r="L2" s="17" t="inlineStr"/>
       <c r="M2" s="17" t="inlineStr">
         <is>
-          <t>Game8, IGN, PC Gamer</t>
+          <t>Game8, Dexerto, gamingpromax</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1015,7 @@
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>R 999</t>
+          <t>999</t>
         </is>
       </c>
       <c r="G3" s="18" t="n">
@@ -1045,7 +1044,7 @@
       <c r="L3" s="17" t="inlineStr"/>
       <c r="M3" s="17" t="inlineStr">
         <is>
-          <t>Game8, IGN</t>
+          <t>Game8</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1072,7 @@
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>R 999</t>
+          <t>999</t>
         </is>
       </c>
       <c r="G4" s="18" t="n">
@@ -1096,7 +1095,7 @@
       </c>
       <c r="K4" s="17" t="inlineStr">
         <is>
-          <t>Comparatively slow acceleration; weaker on very twisty courses.</t>
+          <t>Slow acceleration; weaker on very twisty courses.</t>
         </is>
       </c>
       <c r="L4" s="17" t="inlineStr"/>
@@ -1130,18 +1129,20 @@
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>S2 ~950</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr"/>
+          <t>901-998</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>2700000</v>
+      </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>Autoshow</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+          <t>Autoshow (also Wheelspin / loyalty)</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
         </is>
       </c>
       <c r="J5" s="17" t="inlineStr">
@@ -1151,13 +1152,13 @@
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t>Pricey; rewards smooth inputs.</t>
+          <t>Very expensive; demanding on bumpy streets.</t>
         </is>
       </c>
       <c r="L5" s="17" t="inlineStr"/>
       <c r="M5" s="17" t="inlineStr">
         <is>
-          <t>Game8, multiple tier lists</t>
+          <t>Game8, Dexerto</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1186,7 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>901-998</t>
         </is>
       </c>
       <c r="G6" s="18" t="n">
@@ -1203,7 +1204,7 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>PC Gamer's single favourite; cover car. Slicks + widened track = exceptionally planted. Standout value.</t>
+          <t>PC Gamer's favourite; cover car. Slicks + widened track = exceptionally planted. Standout value.</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
@@ -1242,7 +1243,7 @@
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>901-998</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr"/>
@@ -1297,7 +1298,7 @@
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>801-900</t>
         </is>
       </c>
       <c r="G8" s="18" t="n">
@@ -1315,18 +1316,18 @@
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>Go-to S1. AWD traction, ~600 hp, quick off the line; ideal for bend-heavy tracks. Base game, no DLC.</t>
+          <t>Go-to S1: AWD traction, ~600 hp, quick off the line; bend-heavy tracks. Base game.</t>
         </is>
       </c>
       <c r="K8" s="17" t="inlineStr">
         <is>
-          <t>Heavier than RWD rivals.</t>
+          <t>Heavy; AWD understeer if mistuned.</t>
         </is>
       </c>
       <c r="L8" s="17" t="inlineStr"/>
       <c r="M8" s="17" t="inlineStr">
         <is>
-          <t>Game8, multiple</t>
+          <t>Game8, Dexerto</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1355,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>801-900</t>
         </is>
       </c>
       <c r="G9" s="18" t="n">
@@ -1372,7 +1373,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>Quintessential street racer; slicks + wider base = perfect for tight tracks.</t>
+          <t>Quintessential street racer; slicks + wide base = perfect for tight tracks.</t>
         </is>
       </c>
       <c r="K9" s="17" t="inlineStr">
@@ -1411,7 +1412,7 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>801-900</t>
         </is>
       </c>
       <c r="G10" s="18" t="n">
@@ -1429,18 +1430,18 @@
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t>10 launch stat, strong acceleration; accessible and very tunable.</t>
+          <t>10 launch stat; near-perfect top speed/handling/braking; very tunable.</t>
         </is>
       </c>
       <c r="K10" s="17" t="inlineStr">
         <is>
-          <t>Understeers if front tyres left stock.</t>
+          <t>Tricky at the limit until tuned.</t>
         </is>
       </c>
       <c r="L10" s="17" t="inlineStr"/>
       <c r="M10" s="17" t="inlineStr">
         <is>
-          <t>Game8</t>
+          <t>gamingpromax</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1469,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>701-800</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr"/>
@@ -1477,19 +1478,19 @@
           <t>Autoshow</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
         </is>
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>Cleanest modern-JDM A pick; most flexible platform (road/drift/CC). Well-tuned it punches into S1.</t>
+          <t>Most adaptable A platform (road/drift/CC); well-tuned it punches into S1.</t>
         </is>
       </c>
       <c r="K11" s="17" t="inlineStr">
         <is>
-          <t>Needs tuning to shine.</t>
+          <t>Jack-of-all-trades; not class-leading raw pace.</t>
         </is>
       </c>
       <c r="L11" s="17" t="inlineStr"/>
@@ -1523,7 +1524,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>701-800</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr"/>
@@ -1539,7 +1540,7 @@
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>Traditional A option with better speed/handling balance.</t>
+          <t>Traditional A option with strong speed/handling balance.</t>
         </is>
       </c>
       <c r="K12" s="17" t="inlineStr">
@@ -1560,52 +1561,52 @@
           <t>Road &amp; Street</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>2021 Volkswagen Golf R</t>
+          <t>1993 Jaguar XJ220</t>
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>2021</v>
+        <v>1993</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>701-800</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>Autoshow</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>Tentative</t>
+          <t>Autoshow / Auction House</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>Cited as strongest AWD all-rounder for B-Class road.</t>
+          <t>Excellent for fast, open road events.</t>
         </is>
       </c>
       <c r="K13" s="17" t="inlineStr">
         <is>
-          <t>Early / single-weighted claim — verify.</t>
+          <t>Less agile in tight corners.</t>
         </is>
       </c>
       <c r="L13" s="17" t="inlineStr"/>
       <c r="M13" s="17" t="inlineStr">
         <is>
-          <t>Single source</t>
+          <t>gamingpromax</t>
         </is>
       </c>
     </row>
@@ -1621,182 +1622,184 @@
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>1969 Toyota 2000GT</t>
+          <t>2009 Audi RS 6</t>
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>1969</v>
+        <v>2009</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>601-700</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr"/>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>Barn Find (must be located)</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>Tentative</t>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>Standout B-Class pick.</t>
+          <t>Strong speed + handling; traditional B option.</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
         <is>
-          <t>Barn Find — not buyable until found.</t>
+          <t>Heavy vs hot-hatch rivals.</t>
         </is>
       </c>
       <c r="L14" s="17" t="inlineStr"/>
       <c r="M14" s="17" t="inlineStr">
         <is>
-          <t>Single source</t>
+          <t>Game8</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Drag &amp; Top Speed</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>S2</t>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>2012 Nissan GT-R Black Edition (R35) 'Forza Edition'</t>
+          <t>2021 Volkswagen Golf R</t>
         </is>
       </c>
       <c r="E15" s="16" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>S2 ~850</t>
+          <t>601-700</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr"/>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>Wheelspins / Auction House only (not Autoshow)</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Strong</t>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Tentative</t>
         </is>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>Consensus fastest drag car. Pre-tuned AWD, drag tyres + chute, 10/10/10 speed/accel/launch, ~6s quarter mile.</t>
+          <t>Strong AWD all-rounder for B-Class road.</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
         <is>
-          <t>Near-uncontrollable in corners — straight-line only. Forza Edition, can't be bought outright.</t>
+          <t>Early / single-weighted claim — verify.</t>
         </is>
       </c>
       <c r="L15" s="17" t="inlineStr"/>
       <c r="M15" s="17" t="inlineStr">
         <is>
-          <t>Skycoach, community consensus</t>
+          <t>Single source</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Drag &amp; Top Speed</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>S2</t>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>2020 Koenigsegg Jesko</t>
+          <t>1969 Toyota 2000GT</t>
         </is>
       </c>
       <c r="E16" s="16" t="n">
-        <v>2020</v>
+        <v>1969</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>601-700</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr"/>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>Autoshow</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+          <t>Barn Find (must be located)</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Tentative</t>
         </is>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>Top-speed king for speed-trap / half-mile pulls.</t>
+          <t>Standout classic B-Class pick.</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>Not as quick off the line as the AWD GT-R FE.</t>
+          <t>Barn Find — not buyable until found.</t>
         </is>
       </c>
       <c r="L16" s="17" t="inlineStr"/>
       <c r="M16" s="17" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Single source</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Drag &amp; Top Speed</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>S2</t>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>Hennessey Venom F5</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr"/>
+          <t>1961 Jaguar E-Type S1</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>1961</v>
+      </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>501-600</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr"/>
@@ -1805,59 +1808,59 @@
           <t>Autoshow</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Tentative</t>
         </is>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>Raw-power top-speed pick (community clocked 315+ mph).</t>
+          <t>Cited as best C-class all-rounder; strong balance.</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>Less forgiving than the GT-R FE.</t>
+          <t>Needs tuning to reach the class ceiling.</t>
         </is>
       </c>
       <c r="L17" s="17" t="inlineStr"/>
       <c r="M17" s="17" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Game8</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Drag &amp; Top Speed</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="C18" s="16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>1998 Toyota Supra RZ</t>
+          <t>1965 Toyota Sports 800</t>
         </is>
       </c>
       <c r="E18" s="16" t="n">
-        <v>1998</v>
+        <v>1965</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>100-500</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr"/>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>Autoshow</t>
+          <t>Autoshow (cheap)</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -1867,18 +1870,18 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>Cheapest credible drag starter.</t>
+          <t>~580 kg; sharpest handling on tight, technical D-class tracks.</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
-          <t>Needs upgrades to compete up-class.</t>
+          <t>Very low power; struggles on long straights.</t>
         </is>
       </c>
       <c r="L18" s="17" t="inlineStr"/>
       <c r="M18" s="17" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>gamingpromax</t>
         </is>
       </c>
     </row>
@@ -1888,33 +1891,31 @@
           <t>Drag &amp; Top Speed</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>1994 Mazda MX-5 Miata 'Forza Edition'</t>
+          <t>2019 Toyota Tacoma TRD Pro 'Forza Edition'</t>
         </is>
       </c>
       <c r="E19" s="16" t="n">
-        <v>1994</v>
+        <v>2019</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>S2 ~850</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="n">
-        <v>475000</v>
-      </c>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>Autoshow / Auction House</t>
+          <t>Wheelspin / FE reward</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -1924,25 +1925,25 @@
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>Best accessible drag pick; lightweight AWD. Get accel + launch to 10 via tune.</t>
+          <t>AWD monster launch, dialled for drag out of the box.</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
         <is>
-          <t>Disagreement vs GT-R FE on outright pace.</t>
+          <t>Poor top-end speed.</t>
         </is>
       </c>
       <c r="L19" s="17" t="inlineStr"/>
       <c r="M19" s="17" t="inlineStr">
         <is>
-          <t>GAMES.gg</t>
+          <t>Game8</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Drag &amp; Top Speed</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1951,80 +1952,82 @@
         </is>
       </c>
       <c r="C20" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>Lotus Evija 'Forza Edition'</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr"/>
+          <t>2012 Nissan GT-R Black Edition (R35) 'Forza Edition'</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>2012</v>
+      </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>901-998</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>Wheelspin-exclusive</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+          <t>Wheelspins / Auction House only</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
         </is>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>S2 drift specialist — electric instant torque.</t>
+          <t>Consensus best all-round drag: factory chute, AWD, ~3,000 hp, consistent ~6s quarter mile.</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>Wheelspin-only; twitchier than ICE drifters.</t>
+          <t>RNG to obtain; near-uncontrollable in corners (straight-line only).</t>
         </is>
       </c>
       <c r="L20" s="17" t="inlineStr"/>
       <c r="M20" s="17" t="inlineStr">
         <is>
-          <t>Switchblade</t>
+          <t>Game8, gamingpromax, community</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Drift</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>S1</t>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>2020 Formula Drift #151 Toyota GR Supra</t>
+          <t>1994 Mazda MX-5 Miata 'Forza Edition'</t>
         </is>
       </c>
       <c r="E21" s="16" t="n">
-        <v>2020</v>
+        <v>1994</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>901-998</t>
         </is>
       </c>
       <c r="G21" s="18" t="n">
-        <v>185000</v>
+        <v>500000</v>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>Autoshow</t>
+          <t>Aftermarket spot (Festival KM Drag Meet) / Auction House</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -2034,30 +2037,30 @@
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>Glides and smokes even stock; FD cars outperform any B-class drift build.</t>
+          <t>Best out-of-box drag car; AWD + stock drag tyres, insane launch.</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>Pricier than entry drifters.</t>
+          <t>Falls off on very long top-speed strips.</t>
         </is>
       </c>
       <c r="L21" s="17" t="inlineStr"/>
       <c r="M21" s="17" t="inlineStr">
         <is>
-          <t>Game8, Switchblade</t>
+          <t>Game8</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Drift</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>S1</t>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
         </is>
       </c>
       <c r="C22" s="16" t="n">
@@ -2065,19 +2068,21 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Formula Drift #64 Nissan Z</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr"/>
+          <t>2021 Hennessey Venom F5</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>2021</v>
+      </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>901-998</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr"/>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>Autoshow</t>
+          <t>Autoshow / Auction House</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -2087,69 +2092,69 @@
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>Scores high, holds angle, less twitchy than electric drift cars — good for beginners.</t>
+          <t>Raw top-speed king (community clocked ~315+ mph).</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>Edged out by the #151 Supra at the top.</t>
+          <t>Traction-limited launch; poor for short drags.</t>
         </is>
       </c>
       <c r="L22" s="17" t="inlineStr"/>
       <c r="M22" s="17" t="inlineStr">
         <is>
-          <t>Switchblade</t>
+          <t>Dexerto, community</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Drift</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>2002 Nissan Silvia Spec-R</t>
+          <t>2012 Nissan GT-R Black Edition (R35)</t>
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>801-900</t>
         </is>
       </c>
       <c r="G23" s="18" t="n">
-        <v>44000</v>
+        <v>80000</v>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
           <t>Autoshow</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>Strong</t>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>Unassuming but swings around corners; strong engine + wide drift tyres; clears most challenges.</t>
+          <t>Cheap AWD launch base for drag builds.</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>Outscored by Formula Drift cars in open zones.</t>
+          <t>Stock top end limited.</t>
         </is>
       </c>
       <c r="L23" s="17" t="inlineStr"/>
@@ -2162,122 +2167,126 @@
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Drift</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="C24" s="16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>2022 Mazda MX-5 Miata RF</t>
+          <t>1998 Toyota Supra RZ</t>
         </is>
       </c>
       <c r="E24" s="16" t="n">
-        <v>2022</v>
+        <v>1998</v>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>601-700</t>
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>29000</v>
+        <v>90000</v>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
           <t>Autoshow</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>Strong</t>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>RWD, well-balanced; loves to go sideways and chains drifts without spinning. Any MX-5 works.</t>
+          <t>Best budget build; tunes up to challenge hypercars.</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>Low power ceiling.</t>
+          <t>Needs heavy AWD/power swap to compete up-class.</t>
         </is>
       </c>
       <c r="L24" s="17" t="inlineStr"/>
       <c r="M24" s="17" t="inlineStr">
         <is>
-          <t>Game8</t>
+          <t>gamingpromax</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Drift</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>Toyota AE86 Sprinter Trueno 'Forza Edition'</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr"/>
+          <t>1991 Honda Beat</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>1991</v>
+      </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr"/>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="n">
+        <v>15000</v>
+      </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
           <t>Autoshow</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Tentative</t>
         </is>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>The 'correct' car for Mt. Haruna touge by physics (~980 kg, high-revving).</t>
+          <t>Cheap, light D-class drag entry.</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>Low power — keep power secondary.</t>
+          <t>Tiny power; bottom of the ladder.</t>
         </is>
       </c>
       <c r="L25" s="17" t="inlineStr"/>
       <c r="M25" s="17" t="inlineStr">
         <is>
-          <t>PC Gamer</t>
+          <t>Game8</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Dirt &amp; Rally</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
         </is>
       </c>
       <c r="C26" s="16" t="n">
@@ -2285,132 +2294,126 @@
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>2022 Subaru BRZ 'Forza Edition'</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>2022</v>
-      </c>
+          <t>Lotus Evija 'Forza Edition'</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr"/>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>901-998</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr"/>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>Aftermarket spot at Sotoyama Ski Resort (not Autoshow)</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>Strong</t>
+          <t>Wheelspin-exclusive</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>Perfect 10 off-road rating; a beast in both dirt and cross-country when tuned.</t>
+          <t>S2 drift specialist — electric instant torque.</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>Must be located at the Aftermarket spot.</t>
+          <t>Wheelspin-only; twitchier than ICE drifters.</t>
         </is>
       </c>
       <c r="L26" s="17" t="inlineStr"/>
       <c r="M26" s="17" t="inlineStr">
         <is>
-          <t>Game8</t>
+          <t>Switchblade</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Dirt &amp; Rally</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="17" t="inlineStr">
         <is>
-          <t>2001 Ford #4 Focus RS (rally)</t>
+          <t>2020 Formula Drift #151 Toyota GR Supra</t>
         </is>
       </c>
       <c r="E27" s="16" t="n">
-        <v>2001</v>
+        <v>2020</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>801-900</t>
         </is>
       </c>
       <c r="G27" s="18" t="n">
-        <v>415000</v>
+        <v>185000</v>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
           <t>Autoshow</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
         </is>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>PC Gamer default: scrappy, high speed + accel + off-road handling.</t>
+          <t>Safest overall pick; glides and smokes even stock, checks every box.</t>
         </is>
       </c>
       <c r="K27" s="17" t="inlineStr">
         <is>
-          <t>Costlier than B-class value picks.</t>
+          <t>Premium FD purchase.</t>
         </is>
       </c>
       <c r="L27" s="17" t="inlineStr"/>
       <c r="M27" s="17" t="inlineStr">
         <is>
-          <t>PC Gamer</t>
+          <t>Game8, Switchblade</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>Dirt &amp; Rally</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
         </is>
       </c>
       <c r="C28" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>2004 Subaru Impreza WRX STI</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>2004</v>
-      </c>
+          <t>Formula Drift #64 Forsberg Nissan Z</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr"/>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="n">
-        <v>30000</v>
-      </c>
+          <t>801-900</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr"/>
       <c r="H28" s="17" t="inlineStr">
         <is>
           <t>Autoshow</t>
@@ -2423,12 +2426,12 @@
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>Iconic, dirt-cheap; good general stat spread with headroom before hitting A-rank.</t>
+          <t>Best for most players: easy to buy/tune, 3-stars most drift zones, less twitchy.</t>
         </is>
       </c>
       <c r="K28" s="17" t="inlineStr">
         <is>
-          <t>Needs a rally conversion for higher classes.</t>
+          <t>Spec FD car, less customizable.</t>
         </is>
       </c>
       <c r="L28" s="17" t="inlineStr"/>
@@ -2441,51 +2444,47 @@
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Dirt &amp; Rally</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>2004 Mitsubishi Lancer Evolution VIII MR</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>2004</v>
-      </c>
+          <t>Formula Drift #99 Mazda RX-8</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr"/>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="n">
-        <v>30000</v>
-      </c>
+          <t>801-900</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr"/>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>Autoshow (Welcome Pack version pre-tuned to A)</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>Strong</t>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>Near-identical to the Impreza, slightly higher stats across the board.</t>
+          <t>Rotary drifts very controllable, easy to handle.</t>
         </is>
       </c>
       <c r="K29" s="17" t="inlineStr">
         <is>
-          <t>Same conversion needs up-class.</t>
+          <t>Rotary fuel/heat quirks.</t>
         </is>
       </c>
       <c r="L29" s="17" t="inlineStr"/>
@@ -2498,12 +2497,12 @@
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>Cross-Country</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>S1</t>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="C30" s="16" t="n">
@@ -2511,19 +2510,23 @@
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>Dodge Viper 'Forza Edition' / GTS ACR FE</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr"/>
+          <t>2002 Nissan Silvia Spec-R (S15)</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>2002</v>
+      </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>S1+</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr"/>
+          <t>701-800</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="n">
+        <v>44000</v>
+      </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>Premium edition / VIP only</t>
+          <t>Autoshow</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -2533,25 +2536,25 @@
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>Best S1+ cross-country: incredibly fast and lightweight, nothing comparable right now.</t>
+          <t>Community 'king of sliding'; technical precision, wide drift tyres, clears most challenges.</t>
         </is>
       </c>
       <c r="K30" s="17" t="inlineStr">
         <is>
-          <t>Premium/VIP locked. Free alternative: Subaru BRZ FE.</t>
+          <t>Outscored by Formula Drift cars in open zones.</t>
         </is>
       </c>
       <c r="L30" s="17" t="inlineStr"/>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t>Game8</t>
+          <t>Game8, PC Gamer</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>Cross-Country</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -2564,13 +2567,13 @@
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>Mercedes-Benz X-Class</t>
+          <t>Ford Mustang Dark Horse</t>
         </is>
       </c>
       <c r="E31" s="16" t="inlineStr"/>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>701-800</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr"/>
@@ -2586,108 +2589,102 @@
       </c>
       <c r="J31" s="17" t="inlineStr">
         <is>
-          <t>Best A-Class CC pick; consistent across all CC track types.</t>
+          <t>Best muscle drift: power, aggressive rotation, wide lines.</t>
         </is>
       </c>
       <c r="K31" s="17" t="inlineStr">
         <is>
-          <t>Not the fastest outright.</t>
+          <t>Hard to keep straight; heavy.</t>
         </is>
       </c>
       <c r="L31" s="17" t="inlineStr"/>
       <c r="M31" s="17" t="inlineStr">
         <is>
-          <t>Game8</t>
+          <t>PC Gamer</t>
         </is>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>Cross-Country</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="C32" s="16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>2023 Ford F-150 Raptor R</t>
+          <t>1994 Nissan Silvia K's (S14)</t>
         </is>
       </c>
       <c r="E32" s="16" t="n">
-        <v>2023</v>
+        <v>1994</v>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="n">
-        <v>110000</v>
-      </c>
+          <t>601-700</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr"/>
       <c r="H32" s="17" t="inlineStr">
         <is>
           <t>Autoshow</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
         </is>
       </c>
       <c r="J32" s="17" t="inlineStr">
         <is>
-          <t>Huge power and great for ramming.</t>
+          <t>Most balanced Silvia; SR20DET predictable, clean linked angle, no snap oversteer.</t>
         </is>
       </c>
       <c r="K32" s="17" t="inlineStr">
         <is>
-          <t>Ugly handling on paper — tune handling first, then top speed.</t>
+          <t>Mid power until built (~400-450 hp target).</t>
         </is>
       </c>
       <c r="L32" s="17" t="inlineStr"/>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>Game8</t>
+          <t>Switchblade</t>
         </is>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>Cross-Country</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>2025 Toyota Land Cruiser</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>2025</v>
-      </c>
+          <t>Toyota JZX100 Chaser</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr"/>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="n">
-        <v>70000</v>
-      </c>
+          <t>601-700</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr"/>
       <c r="H33" s="17" t="inlineStr">
         <is>
           <t>Autoshow</t>
@@ -2700,25 +2697,25 @@
       </c>
       <c r="J33" s="17" t="inlineStr">
         <is>
-          <t>Reliable all-terrain.</t>
+          <t>1JZ-GTE, long wheelbase great for long passes / Tokyo expressways.</t>
         </is>
       </c>
       <c r="K33" s="17" t="inlineStr">
         <is>
-          <t>Needs accel + braking tuned for bendy tracks.</t>
+          <t>Heavy; less agile in tight switchbacks.</t>
         </is>
       </c>
       <c r="L33" s="17" t="inlineStr"/>
       <c r="M33" s="17" t="inlineStr">
         <is>
-          <t>Game8</t>
+          <t>Switchblade</t>
         </is>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>Cross-Country</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -2731,45 +2728,1296 @@
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>Ford F-450 (Super Duty)</t>
+          <t>Toyota AE86 Sprinter Trueno 'Forza Edition'</t>
         </is>
       </c>
       <c r="E34" s="16" t="inlineStr"/>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>D-B</t>
+          <t>601-700</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr"/>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>Autoshow</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>Strong</t>
+          <t>Wheelspin / FE reward</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J34" s="17" t="inlineStr">
         <is>
-          <t>Best choice for any race in D-B; consistent across all cross-country tracks.</t>
+          <t>Adds power without changing the chassis balance; the 'correct' touge car (Mt. Haruna).</t>
         </is>
       </c>
       <c r="K34" s="17" t="inlineStr">
         <is>
-          <t>Heavy; not for higher classes.</t>
+          <t>FE acquisition only.</t>
         </is>
       </c>
       <c r="L34" s="17" t="inlineStr"/>
       <c r="M34" s="17" t="inlineStr">
         <is>
+          <t>Switchblade, PC Gamer</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>2022 Mazda MX-5 Miata RF</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>501-600</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J35" s="17" t="inlineStr">
+        <is>
+          <t>Friendliest learner; chains drifts without spinning on drift tyres. Any MX-5 works.</t>
+        </is>
+      </c>
+      <c r="K35" s="17" t="inlineStr">
+        <is>
+          <t>Low stock power; wants forced induction.</t>
+        </is>
+      </c>
+      <c r="L35" s="17" t="inlineStr"/>
+      <c r="M35" s="17" t="inlineStr">
+        <is>
+          <t>PC Gamer</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>Nissan Silvia (S13)</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr"/>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>501-600</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr"/>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow (early career)</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>Forgiving, cheap to upgrade, available early.</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
+        <is>
+          <t>Needs power tuning to shine.</t>
+        </is>
+      </c>
+      <c r="L36" s="17" t="inlineStr"/>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>Switchblade</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>Toyota Sprinter Trueno GT Apex (AE86)</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr"/>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr"/>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow (cheap)</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>~980 kg + high-rev 4A-GE rotates faster than anything in D; holds angle on min throttle.</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>Tiny power ceiling; outclassed once tuned past D.</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="inlineStr"/>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>Switchblade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>Porsche 917 'Forza Edition' (rally conversion)</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr"/>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>901-998</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr"/>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>FE / Wheelspin</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>Tentative</t>
+        </is>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t>Top-tier converted rally option at high PI.</t>
+        </is>
+      </c>
+      <c r="K38" s="17" t="inlineStr">
+        <is>
+          <t>FE-only; needs full conversion.</t>
+        </is>
+      </c>
+      <c r="L38" s="17" t="inlineStr"/>
+      <c r="M38" s="17" t="inlineStr">
+        <is>
           <t>Game8</t>
         </is>
       </c>
     </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>Audi Sport Quattro S1</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr"/>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>801-900</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr"/>
+      <c r="H39" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t>Go-to traditional rally car; iconic AWD turbo.</t>
+        </is>
+      </c>
+      <c r="K39" s="17" t="inlineStr">
+        <is>
+          <t>Older chassis vs converted exotics.</t>
+        </is>
+      </c>
+      <c r="L39" s="17" t="inlineStr"/>
+      <c r="M39" s="17" t="inlineStr">
+        <is>
+          <t>Game8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>Lotus Exige WTAC (rally conversion)</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr"/>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>801-900</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr"/>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow / Aftermarket</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t>Once rally-converted, one of the best dirt-race cars overall.</t>
+        </is>
+      </c>
+      <c r="K40" s="17" t="inlineStr">
+        <is>
+          <t>Requires a full rally conversion.</t>
+        </is>
+      </c>
+      <c r="L40" s="17" t="inlineStr"/>
+      <c r="M40" s="17" t="inlineStr">
+        <is>
+          <t>Game8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>2022 Subaru BRZ 'Forza Edition'</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>701-800</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr"/>
+      <c r="H41" s="17" t="inlineStr">
+        <is>
+          <t>Aftermarket spot at Sotoyama Ski Resort</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J41" s="17" t="inlineStr">
+        <is>
+          <t>Perfect 10 off-road rating; a beast in both dirt and cross-country tuned.</t>
+        </is>
+      </c>
+      <c r="K41" s="17" t="inlineStr">
+        <is>
+          <t>Must be located at the Aftermarket spot.</t>
+        </is>
+      </c>
+      <c r="L41" s="17" t="inlineStr"/>
+      <c r="M41" s="17" t="inlineStr">
+        <is>
+          <t>Game8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>Mitsubishi Lancer Evolution VI</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr"/>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>701-800</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr"/>
+      <c r="H42" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J42" s="17" t="inlineStr">
+        <is>
+          <t>AWD + turbo + balanced chassis; fast and stable on loose dirt.</t>
+        </is>
+      </c>
+      <c r="K42" s="17" t="inlineStr">
+        <is>
+          <t>Needs a rally conversion to fully optimize.</t>
+        </is>
+      </c>
+      <c r="L42" s="17" t="inlineStr"/>
+      <c r="M42" s="17" t="inlineStr">
+        <is>
+          <t>gamingpromax</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>2001 Ford #4 Focus RS (rally)</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>2001</v>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>701-800</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="n">
+        <v>415000</v>
+      </c>
+      <c r="H43" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J43" s="17" t="inlineStr">
+        <is>
+          <t>Scrappy: high speed + accel + off-road handling.</t>
+        </is>
+      </c>
+      <c r="K43" s="17" t="inlineStr">
+        <is>
+          <t>Costlier than B-class value picks.</t>
+        </is>
+      </c>
+      <c r="L43" s="17" t="inlineStr"/>
+      <c r="M43" s="17" t="inlineStr">
+        <is>
+          <t>PC Gamer</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>2004 Subaru Impreza WRX STI</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>601-700</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J44" s="17" t="inlineStr">
+        <is>
+          <t>Iconic, dirt-cheap; great general spread with headroom before hitting A-rank.</t>
+        </is>
+      </c>
+      <c r="K44" s="17" t="inlineStr">
+        <is>
+          <t>Stock power modest; needs conversion up-class.</t>
+        </is>
+      </c>
+      <c r="L44" s="17" t="inlineStr"/>
+      <c r="M44" s="17" t="inlineStr">
+        <is>
+          <t>PC Gamer, Game8</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>2004 Mitsubishi Lancer Evolution VIII MR</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>601-700</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H45" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow (Welcome Pack version pre-tuned to A)</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J45" s="17" t="inlineStr">
+        <is>
+          <t>Reliable AWD out of the box; hard to beat on dirt/rally.</t>
+        </is>
+      </c>
+      <c r="K45" s="17" t="inlineStr">
+        <is>
+          <t>Heavier than tuned rivals.</t>
+        </is>
+      </c>
+      <c r="L45" s="17" t="inlineStr"/>
+      <c r="M45" s="17" t="inlineStr">
+        <is>
+          <t>gamingpromax</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>Ford RS200 Evolution</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr"/>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>601-700</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="inlineStr"/>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow / Auction House</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t>Short wheelbase, light, huge corner manoeuvrability; proven dirt weapon.</t>
+        </is>
+      </c>
+      <c r="K46" s="17" t="inlineStr">
+        <is>
+          <t>Twitchy at high speed.</t>
+        </is>
+      </c>
+      <c r="L46" s="17" t="inlineStr"/>
+      <c r="M46" s="17" t="inlineStr">
+        <is>
+          <t>PC Gamer</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>Toyota Celica GT-Four ST205</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr"/>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>501-600</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr"/>
+      <c r="H47" s="17" t="inlineStr">
+        <is>
+          <t>Prologue starter / Autoshow</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J47" s="17" t="inlineStr">
+        <is>
+          <t>AWD traction, mixed-surface flexibility, best top speed of the starters.</t>
+        </is>
+      </c>
+      <c r="K47" s="17" t="inlineStr">
+        <is>
+          <t>Not a pure dirt specialist.</t>
+        </is>
+      </c>
+      <c r="L47" s="17" t="inlineStr"/>
+      <c r="M47" s="17" t="inlineStr">
+        <is>
+          <t>gamingpromax</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>1970 GMC Jimmy</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>1970</v>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H48" s="17" t="inlineStr">
+        <is>
+          <t>Prologue starter / Autoshow</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J48" s="17" t="inlineStr">
+        <is>
+          <t>Built for rough routes, 9.3 off-road rating; free early.</t>
+        </is>
+      </c>
+      <c r="K48" s="17" t="inlineStr">
+        <is>
+          <t>Slow on clean road.</t>
+        </is>
+      </c>
+      <c r="L48" s="17" t="inlineStr"/>
+      <c r="M48" s="17" t="inlineStr">
+        <is>
+          <t>gamingpromax</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>Ford Bronco R</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr"/>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>901-998</t>
+        </is>
+      </c>
+      <c r="G49" s="16" t="inlineStr"/>
+      <c r="H49" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J49" s="17" t="inlineStr">
+        <is>
+          <t>Factory off-road tyres, perfect 10 off-road rating; excels at huge drops (~6,500 lb durability).</t>
+        </is>
+      </c>
+      <c r="K49" s="17" t="inlineStr">
+        <is>
+          <t>Heavy, ~325 hp, low handling rating (~4).</t>
+        </is>
+      </c>
+      <c r="L49" s="17" t="inlineStr"/>
+      <c r="M49" s="17" t="inlineStr">
+        <is>
+          <t>PC Gamer</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>Dodge Viper 'Forza Edition' / GTS ACR FE</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr"/>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>801-900</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr"/>
+      <c r="H50" s="17" t="inlineStr">
+        <is>
+          <t>Premium edition / VIP only</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J50" s="17" t="inlineStr">
+        <is>
+          <t>Best S1+ CC: incredibly fast and lightweight, nothing comparable for speed.</t>
+        </is>
+      </c>
+      <c r="K50" s="17" t="inlineStr">
+        <is>
+          <t>Paywalled (VIP/Premium). Free alternative: Subaru BRZ FE.</t>
+        </is>
+      </c>
+      <c r="L50" s="17" t="inlineStr"/>
+      <c r="M50" s="17" t="inlineStr">
+        <is>
+          <t>Game8</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>2022 Subaru BRZ 'Forza Edition'</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>801-900</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="inlineStr"/>
+      <c r="H51" s="17" t="inlineStr">
+        <is>
+          <t>Aftermarket spot at Sotoyama Ski Resort</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J51" s="17" t="inlineStr">
+        <is>
+          <t>Best FREE S1+ pick; excellent control on loose surfaces, handles CC well.</t>
+        </is>
+      </c>
+      <c r="K51" s="17" t="inlineStr">
+        <is>
+          <t>RWD-biased vs trucks on the roughest terrain.</t>
+        </is>
+      </c>
+      <c r="L51" s="17" t="inlineStr"/>
+      <c r="M51" s="17" t="inlineStr">
+        <is>
+          <t>Game8</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz X-Class</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr"/>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>701-800</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr"/>
+      <c r="H52" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t>Best A-class CC pick; consistent on all cross-country race types.</t>
+        </is>
+      </c>
+      <c r="K52" s="17" t="inlineStr">
+        <is>
+          <t>Not the fastest outright.</t>
+        </is>
+      </c>
+      <c r="L52" s="17" t="inlineStr"/>
+      <c r="M52" s="17" t="inlineStr">
+        <is>
+          <t>Game8</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>2023 Ford F-150 Raptor R</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>701-800</t>
+        </is>
+      </c>
+      <c r="G53" s="18" t="n">
+        <v>110000</v>
+      </c>
+      <c r="H53" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J53" s="17" t="inlineStr">
+        <is>
+          <t>Huge power and great for ramming.</t>
+        </is>
+      </c>
+      <c r="K53" s="17" t="inlineStr">
+        <is>
+          <t>Ugly handling on paper — tune handling first, then top speed.</t>
+        </is>
+      </c>
+      <c r="L53" s="17" t="inlineStr"/>
+      <c r="M53" s="17" t="inlineStr">
+        <is>
+          <t>Game8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>2025 Toyota Land Cruiser</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>701-800</t>
+        </is>
+      </c>
+      <c r="G54" s="18" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H54" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t>Reliable all-terrain.</t>
+        </is>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
+        <is>
+          <t>Needs accel + braking tuned for bendy tracks.</t>
+        </is>
+      </c>
+      <c r="L54" s="17" t="inlineStr"/>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>Game8</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>Ford F-450 (Super Duty)</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr"/>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>601-700</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="inlineStr"/>
+      <c r="H55" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J55" s="17" t="inlineStr">
+        <is>
+          <t>Game8's best pick across all of D-B; consistent every tier.</t>
+        </is>
+      </c>
+      <c r="K55" s="17" t="inlineStr">
+        <is>
+          <t>Bulky; slow on tarmac; not for higher classes.</t>
+        </is>
+      </c>
+      <c r="L55" s="17" t="inlineStr"/>
+      <c r="M55" s="17" t="inlineStr">
+        <is>
+          <t>Game8</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Ford F-450 (Super Duty)</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="inlineStr"/>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>501-600</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr"/>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J56" s="17" t="inlineStr">
+        <is>
+          <t>Carries straight into C: durable, consistent on all CC track types.</t>
+        </is>
+      </c>
+      <c r="K56" s="17" t="inlineStr">
+        <is>
+          <t>Bulky; slow on tarmac.</t>
+        </is>
+      </c>
+      <c r="L56" s="17" t="inlineStr"/>
+      <c r="M56" s="17" t="inlineStr">
+        <is>
+          <t>Game8</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>Ford F-450 (Super Duty)</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="inlineStr"/>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="inlineStr"/>
+      <c r="H57" s="17" t="inlineStr">
+        <is>
+          <t>Autoshow</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J57" s="17" t="inlineStr">
+        <is>
+          <t>Best D-class CC pick; consistent across every cross-country track.</t>
+        </is>
+      </c>
+      <c r="K57" s="17" t="inlineStr">
+        <is>
+          <t>Bulky; slow on tarmac.</t>
+        </is>
+      </c>
+      <c r="L57" s="17" t="inlineStr"/>
+      <c r="M57" s="17" t="inlineStr">
+        <is>
+          <t>Game8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M34"/>
+  <autoFilter ref="A1:M57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2863,17 +4111,17 @@
       </c>
       <c r="F2" s="24" t="inlineStr">
         <is>
-          <t>2021 Volkswagen Golf R</t>
-        </is>
-      </c>
-      <c r="G2" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>2009 Audi RS 6</t>
+        </is>
+      </c>
+      <c r="G2" s="25" t="inlineStr">
+        <is>
+          <t>1961 Jaguar E-Type S1</t>
+        </is>
+      </c>
+      <c r="H2" s="26" t="inlineStr">
+        <is>
+          <t>1965 Toyota Sports 800</t>
         </is>
       </c>
     </row>
@@ -2883,39 +4131,39 @@
           <t>Drag &amp; Top Speed</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>2019 Toyota Tacoma TRD Pro 'Forza Edition'</t>
+        </is>
+      </c>
+      <c r="C3" s="21" t="inlineStr">
+        <is>
+          <t>2012 Nissan GT-R Black Edition (R35) 'Forza Edition'</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>2012 Nissan GT-R Black Edition (R35)</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
-        <is>
-          <t>2012 Nissan GT-R Black Edition (R35) 'Forza Edition'</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>1998 Toyota Supra RZ</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
-        <is>
-          <t>1998 Toyota Supra RZ</t>
-        </is>
-      </c>
-      <c r="F3" s="24" t="inlineStr">
-        <is>
-          <t>1994 Mazda MX-5 Miata 'Forza Edition'</t>
-        </is>
-      </c>
-      <c r="G3" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H3" s="26" t="inlineStr">
+        <is>
+          <t>1991 Honda Beat</t>
         </is>
       </c>
     </row>
@@ -2942,22 +4190,22 @@
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
-          <t>2002 Nissan Silvia Spec-R</t>
+          <t>2002 Nissan Silvia Spec-R (S15)</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>Toyota AE86 Sprinter Trueno 'Forza Edition'</t>
-        </is>
-      </c>
-      <c r="G4" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>1994 Nissan Silvia K's (S14)</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>2022 Mazda MX-5 Miata RF</t>
+        </is>
+      </c>
+      <c r="H4" s="26" t="inlineStr">
+        <is>
+          <t>Toyota Sprinter Trueno GT Apex (AE86)</t>
         </is>
       </c>
     </row>
@@ -2972,14 +4220,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Porsche 917 'Forza Edition' (rally conversion)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>Audi Sport Quattro S1</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -2992,14 +4240,14 @@
           <t>2004 Subaru Impreza WRX STI</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>Toyota Celica GT-Four ST205</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>1970 GMC Jimmy</t>
         </is>
       </c>
     </row>
@@ -3014,9 +4262,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Ford Bronco R</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -3034,14 +4282,14 @@
           <t>Ford F-450 (Super Duty)</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>Ford F-450 (Super Duty)</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>Ford F-450 (Super Duty)</t>
         </is>
       </c>
     </row>
@@ -3056,7 +4304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3067,7 +4315,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Tuning — reliable specs, not fake codes</t>
         </is>
@@ -3372,581 +4620,360 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>How to get REAL, current codes (in-game)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
+          <t>Where to get tune codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Real, current codes live in-game, and update as the meta shifts:</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
+          <t>Real, current codes live in-game and update as the meta shifts:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>1. Own the car -&gt; Cars tab -&gt; Upgrades &amp; Tuning.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>2. Find Tuning Setups -&gt; Search (Backspace on PC).</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>3. Filter by event type (drag/drift/rally/road) and sort by most downloaded / highest rated.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1">
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>4. Download, test on a fixed stretch, keep if it suits the event.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Web-advertised 'FH6 codes' are largely auto-generated, invented, or recycled FH5 codes that don't transfer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Per-car tune notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>Dexerto — Best tuning codes (Peel P50, BMW M3 &amp; more)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>Dexerto — Garage share codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>ForzaFire — browse all FH6 tunes by car/class/event</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 Tunes — spreadsheet + Discord (Forza Forums)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>r/ForzaHorizon — community posts new tunes after each weekly playlist reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>* = community-sourced pointer, NOT a verified code. Verbatim FH6 share codes aren't reliably published online yet — most web 'codes' are auto-generated, invented, or recycled FH5 codes that don't transfer. Open the in-game Find Tuning Setups marketplace (or the linked tuner sheet), download a top-rated tune, and confirm it on a fixed stretch of road before trusting it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Tune share codes (community-sourced *)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Car</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Share code *</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Best for</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>1962 Peel P50</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>D 100</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="inlineStr">
+        <is>
+          <t>531 816 165</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>Speed on straights</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>Dexerto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>2007 Alfa Romeo 8C Competizione</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>A 635</t>
+        </is>
+      </c>
+      <c r="C41" s="30" t="inlineStr">
+        <is>
+          <t>759 705 340</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>Drifting</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>Dexerto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>2017 Ferrari J50</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>S1 772</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t>145 195 403</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>Dexerto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Per-car tune notes &amp; code source</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>Tune notes</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>Share code / status</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>2018 Ferrari FXX-K Evo</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline. Mech balance ~0.60. Add downforce for touge; brakes + front tyre width before power.</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>2023 Aston Martin Valkyrie</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline; longer final drive for straights, shorter for technical circuits.</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="44" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>2013 McLaren P1</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline; favour speed-zone gearing on open layouts.</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="44" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>2021 Mercedes-AMG One</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline; mech balance 0.60; lean on aero in fast corners.</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="44" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>2025 GR GT Prototype (Toyota)</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline; already planted — minimal alignment tweaks needed.</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="44" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>2020 Koenigsegg Jesko</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>Top-speed gearing (long final drive); soften to settle the rear on corner entry.</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="44" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>2024 Nissan GT-R NISMO</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline; AWD diff ~70% rear; mech balance 0.60.</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="44" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>2023 Porsche 911 GT3 RS</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline; shorter final drive for technical city/mountain routes.</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="44" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>2023 Porsche 911 Turbo S</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline; widen front tyres + brakes before power.</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="44" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>2020 Toyota GR Supra</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline; the workhorse — tune to the event.</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="44" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>2020 BMW M2 Competition Coupe</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline; balanced springs, slight forward brake bias.</t>
-        </is>
-      </c>
-      <c r="E44" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="44" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>2021 Volkswagen Golf R</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline; AWD diff bias rear; keep it under the 700 PI ceiling.</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="44" customHeight="1">
-      <c r="A46" s="17" t="inlineStr">
-        <is>
-          <t>1969 Toyota 2000GT</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>Road &amp; Street</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
-        <is>
-          <t>Road/grip baseline; classic chassis — modest power, lean on handling.</t>
-        </is>
-      </c>
-      <c r="E46" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>Tune code source *</t>
         </is>
       </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>2012 Nissan GT-R Black Edition (R35) 'Forza Edition'</t>
+          <t>2018 Ferrari FXX-K Evo</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Drag &amp; Top Speed</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>Drag tune (comes pre-tuned). Top gear long; tune 1st gear iteratively on the strip.</t>
-        </is>
-      </c>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr"/>
       <c r="E47" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>2020 Koenigsegg Jesko</t>
+          <t>2023 Aston Martin Valkyrie</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>Drag &amp; Top Speed</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t>Top-speed build: longest viable final drive; minimal downforce.</t>
-        </is>
-      </c>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr"/>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>Hennessey Venom F5</t>
+          <t>2013 McLaren P1</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Drag &amp; Top Speed</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="inlineStr">
-        <is>
-          <t>Top-speed gearing; controllable wheelspin off the line.</t>
-        </is>
-      </c>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr"/>
       <c r="E49" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>1998 Toyota Supra RZ</t>
+          <t>2021 Mercedes-AMG One</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>Drag &amp; Top Speed</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr">
-        <is>
-          <t>Drag tune; prioritise launch + 1st-gear tuning on the strip.</t>
-        </is>
-      </c>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr"/>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>1994 Mazda MX-5 Miata 'Forza Edition'</t>
+          <t>2025 GR GT Prototype (Toyota)</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Drag &amp; Top Speed</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>Drag tyres; hard-launch diff with controllable wheelspin; long top gear.</t>
-        </is>
-      </c>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr"/>
       <c r="E51" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>Lotus Evija 'Forza Edition'</t>
+          <t>2020 Koenigsegg Jesko</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Road &amp; Street</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -3954,26 +4981,22 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>Drift tune; manage instant torque with rear PSI + brake bias.</t>
-        </is>
-      </c>
+      <c r="D52" s="17" t="inlineStr"/>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t>2020 Formula Drift #151 Toyota GR Supra</t>
+          <t>2024 Nissan GT-R NISMO</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Road &amp; Street</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -3981,26 +5004,22 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>Drift tune: front tyre near-max PSI, rear low; max front camber, rear ~0, front toe-out; locked accel diff; forward brake bias.</t>
-        </is>
-      </c>
+      <c r="D53" s="17" t="inlineStr"/>
       <c r="E53" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>Formula Drift #64 Nissan Z</t>
+          <t>2023 Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Road &amp; Street</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
@@ -4008,53 +5027,45 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>Drift tune; slightly softer than the #151 for forgiveness.</t>
-        </is>
-      </c>
+      <c r="D54" s="17" t="inlineStr"/>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="55" ht="44" customHeight="1">
       <c r="A55" s="17" t="inlineStr">
         <is>
-          <t>2002 Nissan Silvia Spec-R</t>
+          <t>2023 Porsche 911 Turbo S</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>Drift</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>Drift tune; wide rear drift tyres; stiff rear springs; rear toe-out.</t>
-        </is>
-      </c>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr"/>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="56" ht="44" customHeight="1">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>2022 Mazda MX-5 Miata RF</t>
+          <t>2020 Toyota GR Supra</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Road &amp; Street</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
@@ -4062,53 +5073,45 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>Drift tune; forgiving balance — great learner drifter.</t>
-        </is>
-      </c>
+      <c r="D56" s="17" t="inlineStr"/>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="57" ht="44" customHeight="1">
       <c r="A57" s="17" t="inlineStr">
         <is>
-          <t>Toyota AE86 Sprinter Trueno 'Forza Edition'</t>
+          <t>2020 BMW M2 Competition Coupe</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>Drift</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
-        <is>
-          <t>Stiff rear springs, rear toe-out, 1.5-way or open LSD; keep power secondary to balance.</t>
-        </is>
-      </c>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr"/>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="58" ht="44" customHeight="1">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>2022 Subaru BRZ 'Forza Edition'</t>
+          <t>1993 Jaguar XJ220</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>Dirt &amp; Rally</t>
+          <t>Road &amp; Street</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
@@ -4116,53 +5119,45 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
-        <is>
-          <t>Rally tune: 22-27 PSI, soft springs near minimum, ride height 5-7in off bump stops, center diff 60-70% rear.</t>
-        </is>
-      </c>
+      <c r="D58" s="17" t="inlineStr"/>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="59" ht="44" customHeight="1">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t>2001 Ford #4 Focus RS (rally)</t>
+          <t>2009 Audi RS 6</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>Dirt &amp; Rally</t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>Rally tune; soft, high ride height; shorter gearing.</t>
-        </is>
-      </c>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr"/>
       <c r="E59" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="60" ht="44" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
-          <t>2004 Subaru Impreza WRX STI</t>
+          <t>2021 Volkswagen Golf R</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>Dirt &amp; Rally</t>
+          <t>Road &amp; Street</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -4170,26 +5165,22 @@
           <t>B</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>Rally tune; AWD; build up to the B ceiling, then bump to A when ready.</t>
-        </is>
-      </c>
+      <c r="D60" s="17" t="inlineStr"/>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="61" ht="44" customHeight="1">
       <c r="A61" s="17" t="inlineStr">
         <is>
-          <t>2004 Mitsubishi Lancer Evolution VIII MR</t>
+          <t>1969 Toyota 2000GT</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>Dirt &amp; Rally</t>
+          <t>Road &amp; Street</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -4197,172 +5188,988 @@
           <t>B</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>Rally tune; Welcome Pack copy arrives pre-tuned to A-rank.</t>
-        </is>
-      </c>
+      <c r="D61" s="17" t="inlineStr"/>
       <c r="E61" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="62" ht="44" customHeight="1">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t>Dodge Viper 'Forza Edition' / GTS ACR FE</t>
+          <t>1961 Jaguar E-Type S1</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>Cross-Country</t>
-        </is>
-      </c>
-      <c r="C62" s="12" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>Cross-country tune: suspension for stability + durability; soft, raised ride height.</t>
-        </is>
-      </c>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr"/>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="63" ht="44" customHeight="1">
       <c r="A63" s="17" t="inlineStr">
         <is>
-          <t>Mercedes-Benz X-Class</t>
+          <t>1965 Toyota Sports 800</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>Cross-Country</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>Cross-country tune; prioritise stability and suspension travel.</t>
-        </is>
-      </c>
+          <t>Road &amp; Street</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr"/>
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: search car, filter Road, sort top-rated *</t>
         </is>
       </c>
     </row>
     <row r="64" ht="44" customHeight="1">
       <c r="A64" s="17" t="inlineStr">
         <is>
-          <t>2023 Ford F-150 Raptor R</t>
+          <t>2019 Toyota Tacoma TRD Pro 'Forza Edition'</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>Cross-Country</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>Cross-country tune; fix handling/stability before chasing top speed.</t>
-        </is>
-      </c>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr"/>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: filter Drag, sort top-rated; also YouTube drag-tune videos *</t>
         </is>
       </c>
     </row>
     <row r="65" ht="44" customHeight="1">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t>2025 Toyota Land Cruiser</t>
+          <t>2012 Nissan GT-R Black Edition (R35) 'Forza Edition'</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>Cross-Country</t>
-        </is>
-      </c>
-      <c r="C65" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>Cross-country tune; raise accel + braking for technical CC layouts.</t>
-        </is>
-      </c>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D65" s="17" t="inlineStr"/>
       <c r="E65" s="17" t="inlineStr">
         <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+          <t>In-game Find Tuning Setups: filter Drag, sort top-rated; also YouTube drag-tune videos *</t>
         </is>
       </c>
     </row>
     <row r="66" ht="44" customHeight="1">
       <c r="A66" s="17" t="inlineStr">
         <is>
+          <t>1994 Mazda MX-5 Miata 'Forza Edition'</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr"/>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Drag, sort top-rated; also YouTube drag-tune videos *</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="44" customHeight="1">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>2021 Hennessey Venom F5</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr"/>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Drag, sort top-rated; also YouTube drag-tune videos *</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="44" customHeight="1">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>2012 Nissan GT-R Black Edition (R35)</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr"/>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Drag, sort top-rated; also YouTube drag-tune videos *</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="44" customHeight="1">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>1998 Toyota Supra RZ</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr"/>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Drag, sort top-rated; also YouTube drag-tune videos *</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="44" customHeight="1">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>1991 Honda Beat</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>Drag &amp; Top Speed</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr"/>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Drag, sort top-rated; also YouTube drag-tune videos *</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="44" customHeight="1">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>Lotus Evija 'Forza Edition'</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="inlineStr"/>
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="44" customHeight="1">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>2020 Formula Drift #151 Toyota GR Supra</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr"/>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="44" customHeight="1">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>Formula Drift #64 Forsberg Nissan Z</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr"/>
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="44" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>Formula Drift #99 Mazda RX-8</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr"/>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="44" customHeight="1">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>2002 Nissan Silvia Spec-R (S15)</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="inlineStr"/>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="44" customHeight="1">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>Ford Mustang Dark Horse</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr"/>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="44" customHeight="1">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>1994 Nissan Silvia K's (S14)</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr"/>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="44" customHeight="1">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>Toyota JZX100 Chaser</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr"/>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="44" customHeight="1">
+      <c r="A79" s="17" t="inlineStr">
+        <is>
+          <t>Toyota AE86 Sprinter Trueno 'Forza Edition'</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="inlineStr"/>
+      <c r="E79" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="44" customHeight="1">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>2022 Mazda MX-5 Miata RF</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr"/>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="44" customHeight="1">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>Nissan Silvia (S13)</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="inlineStr"/>
+      <c r="E81" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="44" customHeight="1">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>Toyota Sprinter Trueno GT Apex (AE86)</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr"/>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>JSR Chronic FH6 tune sheet (Forza Forums) + in-game Drift filter, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="44" customHeight="1">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>Porsche 917 'Forza Edition' (rally conversion)</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D83" s="17" t="inlineStr"/>
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Dirt/Rally, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="44" customHeight="1">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>Audi Sport Quattro S1</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr"/>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Dirt/Rally, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="44" customHeight="1">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>Lotus Exige WTAC (rally conversion)</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D85" s="17" t="inlineStr"/>
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Dirt/Rally, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="44" customHeight="1">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>2022 Subaru BRZ 'Forza Edition'</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr"/>
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Dirt/Rally, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="44" customHeight="1">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>Mitsubishi Lancer Evolution VI</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="inlineStr"/>
+      <c r="E87" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Dirt/Rally, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="44" customHeight="1">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>2001 Ford #4 Focus RS (rally)</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr"/>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Dirt/Rally, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="44" customHeight="1">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t>2004 Subaru Impreza WRX STI</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="inlineStr"/>
+      <c r="E89" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Dirt/Rally, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="44" customHeight="1">
+      <c r="A90" s="17" t="inlineStr">
+        <is>
+          <t>2004 Mitsubishi Lancer Evolution VIII MR</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr"/>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Dirt/Rally, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="44" customHeight="1">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t>Ford RS200 Evolution</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D91" s="17" t="inlineStr"/>
+      <c r="E91" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Dirt/Rally, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="44" customHeight="1">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>Toyota Celica GT-Four ST205</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr"/>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Dirt/Rally, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="44" customHeight="1">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>1970 GMC Jimmy</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>Dirt &amp; Rally</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D93" s="17" t="inlineStr"/>
+      <c r="E93" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Dirt/Rally, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="44" customHeight="1">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>Ford Bronco R</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D94" s="17" t="inlineStr"/>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Cross-Country, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="44" customHeight="1">
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>Dodge Viper 'Forza Edition' / GTS ACR FE</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D95" s="17" t="inlineStr"/>
+      <c r="E95" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Cross-Country, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="44" customHeight="1">
+      <c r="A96" s="17" t="inlineStr">
+        <is>
+          <t>2022 Subaru BRZ 'Forza Edition'</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="inlineStr"/>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Cross-Country, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="44" customHeight="1">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz X-Class</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="inlineStr"/>
+      <c r="E97" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Cross-Country, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="44" customHeight="1">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>2023 Ford F-150 Raptor R</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr"/>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Cross-Country, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="44" customHeight="1">
+      <c r="A99" s="17" t="inlineStr">
+        <is>
+          <t>2025 Toyota Land Cruiser</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D99" s="17" t="inlineStr"/>
+      <c r="E99" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Cross-Country, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="44" customHeight="1">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
           <t>Ford F-450 (Super Duty)</t>
         </is>
       </c>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="B100" s="17" t="inlineStr">
         <is>
           <t>Cross-Country</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
-        <is>
-          <t>Cross-country tune; soft long-travel suspension; durability first.</t>
-        </is>
-      </c>
-      <c r="E66" s="17" t="inlineStr">
-        <is>
-          <t>No verified public code — build in-game via Find Tuning Setups (see Tuning sheet)</t>
+      <c r="D100" s="17" t="inlineStr"/>
+      <c r="E100" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Cross-Country, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="44" customHeight="1">
+      <c r="A101" s="17" t="inlineStr">
+        <is>
+          <t>Ford F-450 (Super Duty)</t>
+        </is>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D101" s="17" t="inlineStr"/>
+      <c r="E101" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Cross-Country, sort top-rated *</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="44" customHeight="1">
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t>Ford F-450 (Super Duty)</t>
+        </is>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>Cross-Country</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="inlineStr"/>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>In-game Find Tuning Setups: filter Cross-Country, sort top-rated *</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A33:E66"/>
-  <mergeCells count="16">
+  <autoFilter ref="A46:E102"/>
+  <mergeCells count="21">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="B12:E12"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4373,7 +6180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4381,7 +6188,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Sources &amp; methodology</t>
         </is>
@@ -4404,77 +6211,77 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>• Game8 (per-class + off-road/CC guides)</t>
+          <t>• Game8 (per-class + per-discipline guides)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>• grindout (cites Game8 + IGN consensus)</t>
+          <t>• Dexerto wiki (per-class tier lists)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>• IGN</t>
+          <t>• grindout (cites Game8 + IGN consensus)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>• fh6guide</t>
+          <t>• gamingpromax (per-class + Mechanical Balance)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>• fandomwire</t>
+          <t>• Switchblade (drift)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>• gamingpromax (Mechanical Balance)</t>
+          <t>• IGN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>• forza.guide</t>
+          <t>• fh6guide</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>• GAMES.gg</t>
+          <t>• fandomwire</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>• skycoach</t>
+          <t>• forza.guide</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>• Dexerto wiki</t>
+          <t>• GAMES.gg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>• Switchblade (drift)</t>
+          <t>• skycoach</t>
         </is>
       </c>
     </row>
@@ -4485,95 +6292,109 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>• JSR Chronic tune sheet (Forza Forums)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Treated with caution (SEO farms / auto-generated)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>• ggwtb</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>• fh6hub</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>• xmodhub</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>• narcosis</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>• armadaboost</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>• gamerstation (calculator output)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>(Cross-checked only — never used as a sole basis. Fabricated 'telemetry' disregarded.)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Confidence key</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Multiple independent reputable sources agree.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Appears across guides but with disagreement or single-source weighting.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Tentative</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Early / contested; verify in-game before committing credits.</t>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Early / contested / snippet-only; verify in-game before committing credits.</t>
         </is>
       </c>
     </row>
@@ -4583,69 +6404,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" s="15" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D1" s="15" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>Seed</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>Seeded 33 cars from the curated launch-window guide.</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>Curated (PC Gamer, Game8, IGN, et al.)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>